--- a/data/petrol_state_weekly_prices.xlsx
+++ b/data/petrol_state_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2149,6 +2149,35 @@
         <v>209.1</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C60" t="n">
+        <v>211</v>
+      </c>
+      <c r="D60" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="E60" t="n">
+        <v>212.6</v>
+      </c>
+      <c r="F60" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>232.4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>215</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_state_weekly_prices.xlsx
+++ b/data/petrol_state_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,6 +2178,35 @@
         <v>215</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C61" t="n">
+        <v>229</v>
+      </c>
+      <c r="D61" t="n">
+        <v>225.1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>228.2</v>
+      </c>
+      <c r="F61" t="n">
+        <v>224.1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>226.3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="I61" t="n">
+        <v>231.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_state_weekly_prices.xlsx
+++ b/data/petrol_state_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2207,6 +2207,35 @@
         <v>231.4</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C62" t="n">
+        <v>239.4</v>
+      </c>
+      <c r="D62" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>235.3</v>
+      </c>
+      <c r="G62" t="n">
+        <v>234.3</v>
+      </c>
+      <c r="H62" t="n">
+        <v>254.2</v>
+      </c>
+      <c r="I62" t="n">
+        <v>243.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_state_weekly_prices.xlsx
+++ b/data/petrol_state_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2236,6 +2236,35 @@
         <v>243.2</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C63" t="n">
+        <v>238.4</v>
+      </c>
+      <c r="D63" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="E63" t="n">
+        <v>238.4</v>
+      </c>
+      <c r="F63" t="n">
+        <v>234.8</v>
+      </c>
+      <c r="G63" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="I63" t="n">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_state_weekly_prices.xlsx
+++ b/data/petrol_state_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2265,6 +2265,35 @@
         <v>244</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C64" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>240.9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>240.1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>237.7</v>
+      </c>
+      <c r="G64" t="n">
+        <v>239.2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>256.6</v>
+      </c>
+      <c r="I64" t="n">
+        <v>249.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_state_weekly_prices.xlsx
+++ b/data/petrol_state_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2294,6 +2294,35 @@
         <v>249.8</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C65" t="n">
+        <v>242.5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>242.4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>241.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>238.9</v>
+      </c>
+      <c r="G65" t="n">
+        <v>240.1</v>
+      </c>
+      <c r="H65" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="I65" t="n">
+        <v>251.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_state_weekly_prices.xlsx
+++ b/data/petrol_state_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2323,6 +2323,35 @@
         <v>251.6</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C66" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="D66" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="E66" t="n">
+        <v>239.2</v>
+      </c>
+      <c r="F66" t="n">
+        <v>235.2</v>
+      </c>
+      <c r="G66" t="n">
+        <v>233.3</v>
+      </c>
+      <c r="H66" t="n">
+        <v>257</v>
+      </c>
+      <c r="I66" t="n">
+        <v>249.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
